--- a/Images/1/25StatisticalSeries.xlsx
+++ b/Images/1/25StatisticalSeries.xlsx
@@ -422,66 +422,66 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
         <v>3</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="B3">
-        <v>0.04</v>
+        <v>0.07999999999999999</v>
       </c>
       <c r="C3">
-        <v>0.16</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="D3">
         <v>0.12</v>
       </c>
       <c r="E3">
-        <v>0.03999999999999998</v>
+        <v>0.2</v>
       </c>
       <c r="F3">
         <v>0.04000000000000004</v>
       </c>
       <c r="G3">
+        <v>0.1599999999999999</v>
+      </c>
+      <c r="H3">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="I3">
+        <v>0.07999999999999996</v>
+      </c>
+      <c r="J3">
         <v>0.12</v>
-      </c>
-      <c r="H3">
-        <v>0.07999999999999996</v>
-      </c>
-      <c r="I3">
-        <v>0.12</v>
-      </c>
-      <c r="J3">
-        <v>0.28</v>
       </c>
     </row>
   </sheetData>

--- a/Images/1/25StatisticalSeries.xlsx
+++ b/Images/1/25StatisticalSeries.xlsx
@@ -422,28 +422,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -454,28 +454,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="B3">
-        <v>0.07999999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="C3">
-        <v>0.08000000000000002</v>
+        <v>0.16</v>
       </c>
       <c r="D3">
         <v>0.12</v>
       </c>
       <c r="E3">
-        <v>0.2</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="F3">
         <v>0.04000000000000004</v>
       </c>
       <c r="G3">
-        <v>0.1599999999999999</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.08000000000000007</v>
+        <v>0.12</v>
       </c>
       <c r="I3">
         <v>0.07999999999999996</v>

--- a/Images/1/25StatisticalSeries.xlsx
+++ b/Images/1/25StatisticalSeries.xlsx
@@ -16,50 +16,53 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>[ 2.000000,
- 2.400000 )</t>
-  </si>
-  <si>
-    <t>[ 2.400000,
- 2.800000 )</t>
-  </si>
-  <si>
-    <t>[ 2.800000,
- 3.200000 )</t>
-  </si>
-  <si>
-    <t>[ 3.200000,
- 3.600000 )</t>
-  </si>
-  <si>
-    <t>[ 3.600000,
- 4.000000 )</t>
-  </si>
-  <si>
-    <t>[ 4.000000,
- 4.400000 )</t>
-  </si>
-  <si>
-    <t>[ 4.400000,
- 4.800000 )</t>
-  </si>
-  <si>
-    <t>[ 4.800000,
- 5.200000 )</t>
-  </si>
-  <si>
-    <t>[ 5.200000,
- 5.600000 )</t>
-  </si>
-  <si>
-    <t>[ 5.600000,
- 6.000000 ]</t>
+    <t>[ 2.0,
+ 2.4 )</t>
+  </si>
+  <si>
+    <t>[ 2.4,
+ 2.8 )</t>
+  </si>
+  <si>
+    <t>[ 2.8,
+ 3.2 )</t>
+  </si>
+  <si>
+    <t>[ 3.2,
+ 3.6 )</t>
+  </si>
+  <si>
+    <t>[ 3.6,
+ 4.0 )</t>
+  </si>
+  <si>
+    <t>[ 4.0,
+ 4.4 )</t>
+  </si>
+  <si>
+    <t>[ 4.4,
+ 4.8 )</t>
+  </si>
+  <si>
+    <t>[ 4.8,
+ 5.2 )</t>
+  </si>
+  <si>
+    <t>[ 5.2,
+ 5.6 )</t>
+  </si>
+  <si>
+    <t>[ 5.6,
+ 6.0 ]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -77,7 +80,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -85,12 +88,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -385,103 +404,117 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C2" s="1">
+        <v>0.07999999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.07999999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.04000000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2">
+      <c r="B10">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3">
-        <v>0.08</v>
-      </c>
-      <c r="B3">
-        <v>0.24</v>
-      </c>
-      <c r="C3">
-        <v>0.16</v>
-      </c>
-      <c r="D3">
-        <v>0.12</v>
-      </c>
-      <c r="E3">
-        <v>0.04000000000000004</v>
-      </c>
-      <c r="F3">
-        <v>0.04000000000000004</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0.12</v>
-      </c>
-      <c r="I3">
+      <c r="C10" s="1">
         <v>0.07999999999999996</v>
-      </c>
-      <c r="J3">
-        <v>0.12</v>
       </c>
     </row>
   </sheetData>
